--- a/research/traditional_assets/database/data/malaysia/malaysia_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.281</v>
+        <v>0.126</v>
       </c>
       <c r="E2">
-        <v>0.268</v>
+        <v>-0.0017</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>109.8</v>
+        <v>72.3</v>
       </c>
       <c r="L2">
-        <v>0.2659883720930232</v>
+        <v>0.225585023400936</v>
       </c>
       <c r="M2">
-        <v>33.4</v>
+        <v>23.6</v>
       </c>
       <c r="N2">
-        <v>0.03626886741231404</v>
+        <v>0.02343594836146971</v>
       </c>
       <c r="O2">
-        <v>0.3041894353369763</v>
+        <v>0.326417704011065</v>
       </c>
       <c r="P2">
-        <v>33.4</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.03626886741231404</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.3041894353369763</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>23.6</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>127</v>
+        <v>225.5</v>
       </c>
       <c r="V2">
-        <v>0.1379085677055055</v>
+        <v>0.2239324726911619</v>
       </c>
       <c r="W2">
-        <v>0.05153477893551112</v>
+        <v>0.0341375891212994</v>
       </c>
       <c r="X2">
-        <v>0.08980000172303225</v>
+        <v>0.09815358642606971</v>
       </c>
       <c r="Y2">
-        <v>-0.03826522278752113</v>
+        <v>-0.06401599730477031</v>
       </c>
       <c r="Z2">
-        <v>0.1360535249332586</v>
+        <v>0.0954011013543682</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05097068574115827</v>
+        <v>0.06847167561651769</v>
       </c>
       <c r="AC2">
-        <v>-0.05097068574115827</v>
+        <v>-0.06847167561651769</v>
       </c>
       <c r="AD2">
-        <v>1404</v>
+        <v>1398.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1404</v>
+        <v>1398.3</v>
       </c>
       <c r="AG2">
-        <v>1277</v>
+        <v>1172.8</v>
       </c>
       <c r="AH2">
-        <v>0.6038969418039485</v>
+        <v>0.5813412048393132</v>
       </c>
       <c r="AI2">
-        <v>0.3986484567988869</v>
+        <v>0.4309223704890752</v>
       </c>
       <c r="AJ2">
-        <v>0.5810091450930434</v>
+        <v>0.5380310120194512</v>
       </c>
       <c r="AK2">
-        <v>0.3761524639901028</v>
+        <v>0.388421540703451</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.281</v>
+        <v>0.126</v>
       </c>
       <c r="E3">
-        <v>0.268</v>
+        <v>-0.0017</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +728,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>109.8</v>
+        <v>72.3</v>
       </c>
       <c r="L3">
-        <v>0.2659883720930232</v>
+        <v>0.225585023400936</v>
       </c>
       <c r="M3">
-        <v>33.4</v>
+        <v>23.6</v>
       </c>
       <c r="N3">
-        <v>0.03626886741231404</v>
+        <v>0.02343594836146971</v>
       </c>
       <c r="O3">
-        <v>0.3041894353369763</v>
+        <v>0.326417704011065</v>
       </c>
       <c r="P3">
-        <v>33.4</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.03626886741231404</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.3041894353369763</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>23.6</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>127</v>
+        <v>225.5</v>
       </c>
       <c r="V3">
-        <v>0.1379085677055055</v>
+        <v>0.2239324726911619</v>
       </c>
       <c r="W3">
-        <v>0.05153477893551112</v>
+        <v>0.0341375891212994</v>
       </c>
       <c r="X3">
-        <v>0.08980000172303225</v>
+        <v>0.09815358642606971</v>
       </c>
       <c r="Y3">
-        <v>-0.03826522278752113</v>
+        <v>-0.06401599730477031</v>
       </c>
       <c r="Z3">
-        <v>0.1360535249332586</v>
+        <v>0.0954011013543682</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05097068574115827</v>
+        <v>0.06847167561651769</v>
       </c>
       <c r="AC3">
-        <v>-0.05097068574115827</v>
+        <v>-0.06847167561651769</v>
       </c>
       <c r="AD3">
-        <v>1404</v>
+        <v>1398.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1404</v>
+        <v>1398.3</v>
       </c>
       <c r="AG3">
-        <v>1277</v>
+        <v>1172.8</v>
       </c>
       <c r="AH3">
-        <v>0.6038969418039485</v>
+        <v>0.5813412048393132</v>
       </c>
       <c r="AI3">
-        <v>0.3986484567988869</v>
+        <v>0.4309223704890752</v>
       </c>
       <c r="AJ3">
-        <v>0.5810091450930434</v>
+        <v>0.5380310120194512</v>
       </c>
       <c r="AK3">
-        <v>0.3761524639901028</v>
+        <v>0.388421540703451</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/malaysia/malaysia_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.126</v>
+        <v>0.017</v>
       </c>
       <c r="E2">
-        <v>-0.0017</v>
+        <v>-0.096</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>72.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="L2">
-        <v>0.225585023400936</v>
+        <v>0.2972202423378474</v>
       </c>
       <c r="M2">
-        <v>23.6</v>
+        <v>129.8</v>
       </c>
       <c r="N2">
-        <v>0.02343594836146971</v>
+        <v>0.101995913877102</v>
       </c>
       <c r="O2">
-        <v>0.326417704011065</v>
+        <v>1.556354916067146</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>129.8</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.101995913877102</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.556354916067146</v>
       </c>
       <c r="S2">
-        <v>23.6</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>225.5</v>
+        <v>229.6</v>
       </c>
       <c r="V2">
-        <v>0.2239324726911619</v>
+        <v>0.1804180418041804</v>
       </c>
       <c r="W2">
-        <v>0.0341375891212994</v>
+        <v>0.04516408534604138</v>
       </c>
       <c r="X2">
-        <v>0.09815358642606971</v>
+        <v>0.07414450430981163</v>
       </c>
       <c r="Y2">
-        <v>-0.06401599730477031</v>
+        <v>-0.02898041896377026</v>
       </c>
       <c r="Z2">
-        <v>0.0954011013543682</v>
+        <v>0.09392468619246865</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06847167561651769</v>
+        <v>0.05788085440314206</v>
       </c>
       <c r="AC2">
-        <v>-0.06847167561651769</v>
+        <v>-0.05788085440314206</v>
       </c>
       <c r="AD2">
-        <v>1398.3</v>
+        <v>1508.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1398.3</v>
+        <v>1508.3</v>
       </c>
       <c r="AG2">
-        <v>1172.8</v>
+        <v>1278.7</v>
       </c>
       <c r="AH2">
-        <v>0.5813412048393132</v>
+        <v>0.5423783667158115</v>
       </c>
       <c r="AI2">
-        <v>0.4309223704890752</v>
+        <v>0.4497420759161523</v>
       </c>
       <c r="AJ2">
-        <v>0.5380310120194512</v>
+        <v>0.5011954689766002</v>
       </c>
       <c r="AK2">
-        <v>0.388421540703451</v>
+        <v>0.409301878941135</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.126</v>
+        <v>0.017</v>
       </c>
       <c r="E3">
-        <v>-0.0017</v>
+        <v>-0.096</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +728,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>72.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="L3">
-        <v>0.225585023400936</v>
+        <v>0.2972202423378474</v>
       </c>
       <c r="M3">
-        <v>23.6</v>
+        <v>129.8</v>
       </c>
       <c r="N3">
-        <v>0.02343594836146971</v>
+        <v>0.101995913877102</v>
       </c>
       <c r="O3">
-        <v>0.326417704011065</v>
+        <v>1.556354916067146</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>129.8</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.101995913877102</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>1.556354916067146</v>
       </c>
       <c r="S3">
-        <v>23.6</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>225.5</v>
+        <v>229.6</v>
       </c>
       <c r="V3">
-        <v>0.2239324726911619</v>
+        <v>0.1804180418041804</v>
       </c>
       <c r="W3">
-        <v>0.0341375891212994</v>
+        <v>0.04516408534604138</v>
       </c>
       <c r="X3">
-        <v>0.09815358642606971</v>
+        <v>0.07414450430981163</v>
       </c>
       <c r="Y3">
-        <v>-0.06401599730477031</v>
+        <v>-0.02898041896377026</v>
       </c>
       <c r="Z3">
-        <v>0.0954011013543682</v>
+        <v>0.09392468619246865</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06847167561651769</v>
+        <v>0.05788085440314206</v>
       </c>
       <c r="AC3">
-        <v>-0.06847167561651769</v>
+        <v>-0.05788085440314206</v>
       </c>
       <c r="AD3">
-        <v>1398.3</v>
+        <v>1508.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1398.3</v>
+        <v>1508.3</v>
       </c>
       <c r="AG3">
-        <v>1172.8</v>
+        <v>1278.7</v>
       </c>
       <c r="AH3">
-        <v>0.5813412048393132</v>
+        <v>0.5423783667158115</v>
       </c>
       <c r="AI3">
-        <v>0.4309223704890752</v>
+        <v>0.4497420759161523</v>
       </c>
       <c r="AJ3">
-        <v>0.5380310120194512</v>
+        <v>0.5011954689766002</v>
       </c>
       <c r="AK3">
-        <v>0.388421540703451</v>
+        <v>0.409301878941135</v>
       </c>
       <c r="AL3">
         <v>0</v>
